--- a/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/4 Tutorial Answers/Tutorial Answers.xlsx
+++ b/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/4 Tutorial Answers/Tutorial Answers.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimailderbyac-my.sharepoint.com/personal/tcsr529_derby_ac_uk/Documents/_Teaching/202526/5CM522 - Operational Research/Lectures/Semester 2/Week 1 - Introduction to Simulation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="214" documentId="11_F25DC773A252ABDACC104844319B7A1C5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0FF443-F4E0-4454-8C45-E83D72CE4764}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -16,7 +11,7 @@
     <sheet name="Q2" sheetId="1" r:id="rId1"/>
     <sheet name="Q3" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6425,8 +6420,8 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>A2*B2+A3*B3+A4*B4+A5*B5</f>
-        <v>12.5</v>
+        <f>A2*B2+A3*B3+A4*B4+A5*B5+A6*B6+A7*B7</f>
+        <v>15.15</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
